--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_939_Israel_Mediterranean.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_939_Israel_Mediterranean.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R0432c5c7703145f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Reb572468452d48d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rc2d81ac843494f22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R4eff0abb136a46b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rae2fab7a6a9644de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Ra9b5a9dc68f345ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R8f701c92af45400a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R0ab5608fbaf24b42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R1930faa3fc794084"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R09e2f60713fa40fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R7f3e370dd85940a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R50e4d47222d04103"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ939CommercialTable" displayName="EEZ939CommercialTable" ref="A1:O10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O10"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ939CommercialTable" displayName="EEZ939CommercialTable" ref="A1:E10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E10"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ939FunctionalTable" displayName="EEZ939FunctionalTable" ref="A1:O19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O19"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ939FunctionalTable" displayName="EEZ939FunctionalTable" ref="A1:E19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E19"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ939ValidationTable" displayName="EEZ939ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ939ValidationTable" displayName="EEZ939ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -4044,7 +3998,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd917a6ababe94a9d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc6775aa83ad448fe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4054,20 +4008,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -4075,552 +4019,193 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>14.40995071</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>14.40995071</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$51,A2,'Species'!$U$2:$U$51))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>1856.3612542077653</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>1856.3612542077653</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>82.366179984</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.218085199096029</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>165.22859088596206</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>82.366179984</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>179.21544200909733</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$51,A3,'Species'!$U$2:$U$51))</x:f>
-        <x:v>14761.291352433425</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.218085199096029</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>165.22859088596206</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>13609.247855415853</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>1152.043497017572</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0846515185304022</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.08465151853040223</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>15.093292579</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.713988498919299</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>517.593124755635</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>15.093292579</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>635.0728330496759</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$51,A4,'Species'!$U$2:$U$51))</x:f>
-        <x:v>9585.340078193178</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.713988498919299</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>517.593124755635</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>7812.184468815647</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>1773.1556093775307</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.2269730849873732</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.22697308498737317</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>45.346909718</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>2.772747138953783</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>59.25802037320409</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>45.346909718</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>59.72291564987061</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$51,A5,'Species'!$U$2:$U$51))</x:f>
-        <x:v>2708.2496640704117</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>2.772747138953783</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>59.25802037320409</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>2687.1680999310906</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>21.081564139321017</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.007845271808586</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.00784527180858601</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>956.1224758179999</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.4280650393559813</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>267.9569583499836</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>956.1224758179999</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>342.26598787430754</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$51,A6,'Species'!$U$2:$U$51))</x:f>
-        <x:v>327248.20371467643</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.4280650393559813</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>267.9569583499836</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>256199.670430247</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>71048.53328442943</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.2773170362206736</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.27731703622067355</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>1322.894016106</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.655091331044981</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>451.95097854397875</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>1322.894016106</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>782.9824407586028</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$51,A7,'Species'!$U$2:$U$51))</x:f>
-        <x:v>1035802.7855956263</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.655091331044981</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>451.95097854397875</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>597883.2450890807</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>437919.5405065457</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.7324499291518005</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.7324499291518005</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>9.276765668</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.51</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>323.5936569296281</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>9.276765668</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>323.5936569296281</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$51,A8,'Species'!$U$2:$U$51))</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>3001.902526987344</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.51</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>323.5936569296281</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
-        <x:v>3001.902526987344</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>25.342747017</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.0499292212517926</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1121.8356092647298</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>25.342747017</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1121.8764890564748</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$51,A9,'Species'!$U$2:$U$51))</x:f>
-        <x:v>28431.43204647841</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.0499292212517926</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1121.8356092647298</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>28430.39604025811</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>1.036006220299896</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0000364400910502</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.000036440091050187514</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>50.061711187</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.480956198882838</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>3026.6081617218997</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>50.061711187</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>3029.5199020760206</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$51,A10,'Species'!$U$2:$U$51))</x:f>
-        <x:v>151662.95037299825</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.480956198882838</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>3026.6081617218997</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>151517.18366833872</x:v>
       </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>145.76670465953066</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0009620473475709</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.0009620473475708505</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G10">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O10">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R584e64e604c6420e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8ffe78606b4461b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4630,20 +4215,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -4651,1038 +4226,364 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>145.166963638</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.986188869922639</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>968.6990412938402</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>145.166963638</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>988.4727453400322</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$51,A2,'Species'!$U$2:$U$51))</x:f>
-        <x:v>143493.5870799305</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.986188869922639</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>968.6990412938402</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>140623.09850366836</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>2870.4885762621416</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0204126392236141</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.020412639223614183</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>50.359802204</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.848125646169585</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>704.8969739161137</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>50.359802204</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>749.2440219762807</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$51,A3,'Species'!$U$2:$U$51))</x:f>
-        <x:v>37731.780749254925</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.848125646169585</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>704.8969739161137</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>35498.47218061363</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>2233.308568641296</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0629128081140615</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.06291280811406151</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>15.780261419000002</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.122038969824115</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1324.4603754618174</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>15.780261419000002</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1397.090334976244</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$51,A4,'Species'!$U$2:$U$51))</x:f>
-        <x:v>22046.450711883415</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.122038969824115</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1324.4603754618174</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>20900.330963894376</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>1146.1197479890398</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.054837397071318</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.054837397071318066</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>97.74653170000002</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.4851312855172125</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>3055.8447434749114</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>97.74653170000002</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>3061.015379908898</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$51,A5,'Species'!$U$2:$U$51))</x:f>
-        <x:v>299203.6368664527</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.4851312855172125</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>3055.8447434749114</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>298698.22508834885</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>505.41177810385125</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.001692048146434</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.0016920481464339494</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>0.0077988169999999996</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.82</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>660.6934480075957</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>0.0077988169999999996</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>660.6934480075957</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$51,A6,'Species'!$U$2:$U$51))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>5.152627294110253</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.82</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>660.6934480075957</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>5.152627294110253</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>129.91235035399998</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.8898749633448575</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>776.0236614010671</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>129.91235035399998</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1415.1691390870633</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$51,A7,'Species'!$U$2:$U$51))</x:f>
-        <x:v>183847.9490072471</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.8898749633448575</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>776.0236614010671</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>100815.05778292929</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>83032.89122431782</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.8236159662091422</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.8236159662091423</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>25.3349482</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.05</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1122.018454301963</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>25.3349482</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1122.018454301963</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$51,A8,'Species'!$U$2:$U$51))</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>28426.2794191843</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.05</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1122.018454301963</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
-        <x:v>28426.2794191843</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>0.20948149700000002</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>2.51313393893686</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>32.59372064276819</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>0.20948149700000002</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>37.80257842101243</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$51,A9,'Species'!$U$2:$U$51))</x:f>
-        <x:v>7.91894071809358</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>2.51313393893686</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>32.59372064276819</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>6.827781393046883</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>1.0911593250466973</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.1598116961034937</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.1598116961034937</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>9.276765668</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.51</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>323.5936569296281</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>9.276765668</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>323.5936569296281</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$51,A10,'Species'!$U$2:$U$51))</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>3001.902526987344</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.51</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>323.5936569296281</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
-        <x:v>3001.902526987344</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>422.0158861329999</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.401854445133407</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>252.26351633886017</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>422.0158861329999</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>263.4685715310361</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$51,A11,'Species'!$U$2:$U$51))</x:f>
-        <x:v>111187.92268286589</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.401854445133407</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>252.26351633886017</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>106459.21138677058</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>4728.711296095309</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.044418056779659</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.044418056779659126</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>765.7537955749999</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.2506818622578</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>178.10735831989035</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>765.7537955749999</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>188.0058338734614</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$51,A12,'Species'!$U$2:$U$51))</x:f>
-        <x:v>143966.18087884595</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.2506818622578</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>178.10735831989035</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>136386.3856532926</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>7579.79522555336</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0555758933653534</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.05557589336535345</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>247.993708831</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.057647731017976</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>1141.9516885441635</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>247.993708831</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>1251.0391337252693</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$51,A13,'Species'!$U$2:$U$51))</x:f>
-        <x:v>310249.8346652509</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.057647731017976</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>1141.9516885441635</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>283196.83454789006</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>27053.000117360847</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0955271981078094</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.09552719810780952</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>322.286062915</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.5920073371608083</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>390.84749888511055</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>322.286062915</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>672.7365107531963</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$51,A14,'Species'!$U$2:$U$51))</x:f>
-        <x:v>216813.60142982219</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.5920073371608083</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>390.84749888511055</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>125964.70161585714</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>90848.89981396505</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.7212250626450774</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.7212250626450775</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>82.156698487</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.219882669637199</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>165.91386087799546</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>82.156698487</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>179.57601368377553</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$51,A15,'Species'!$U$2:$U$51))</x:f>
-        <x:v>14753.372411715332</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.219882669637199</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>165.91386087799546</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>13630.935042967538</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>1122.4373687477946</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0823448549354566</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.08234485493545667</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>46.14751796</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.58</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>380.1893963205613</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>46.14751796</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>380.1893963205613</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$51,A16,'Species'!$U$2:$U$51))</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>17544.79699490466</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.58</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>380.1893963205613</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
-        <x:v>17544.79699490466</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>59.756860427999996</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>2.854073317566161</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>71.4616957480972</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>59.756860427999996</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>76.38639121240308</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$51,A17,'Species'!$U$2:$U$51))</x:f>
-        <x:v>4564.6109182781765</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>2.854073317566161</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>71.4616957480972</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>4270.326578767245</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>294.2843395109312</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0689137783920697</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.06891377839206972</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>85.915322382</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.515457198555054</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>327.6854805090161</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>85.915322382</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>333.2141208707226</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$51,A18,'Species'!$U$2:$U$51))</x:f>
-        <x:v>28628.198616842845</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.515457198555054</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>327.6854805090161</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>28153.203697832694</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>474.9949190101506</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.016871789232524</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.016871789232524075</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>15.093292579</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.713988498919299</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>517.593124755635</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>15.093292579</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>635.0728330496759</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$51,A19,'Species'!$U$2:$U$51))</x:f>
-        <x:v>9585.340078193178</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.713988498919299</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>517.593124755635</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>7812.184468815647</x:v>
       </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>1773.1556093775307</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.2269730849873732</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.22697308498737317</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G19">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O19">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a3f953864874944"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55deabaf8a6b4ccb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5857,7 +4758,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -5956,7 +4857,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>1575058.5166056715</x:v>
+        <x:v>1062997.3594332822</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5970,7 +4871,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>1575058.5166056715</x:v>
+        <x:v>1351393.9268614114</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5984,7 +4885,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-2.3283064365386963e-10</x:v>
+        <x:v>-512061.15717238956</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5998,7 +4899,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-2.3283064365386963e-10</x:v>
+        <x:v>-223664.5897442603</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6009,9 +4910,9 @@
         <x:v>EEZ_939</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -6023,47 +4924,19 @@
         <x:v>EEZ_939</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_939</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_939</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76c3f7cc0a3542c7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf140429be7614f7f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6110,7 +4983,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
